--- a/گزارش مرجع.xlsx
+++ b/گزارش مرجع.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kazemipour.s\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\پروژه\TRANSFER QC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7884F9C-5530-42E7-9F5C-5FA18E49E182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E87572-2BFF-44D0-8582-4143B42A34B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AE2EE935-E2E8-4CB4-A33F-AA5BDDD6AC28}"/>
+    <workbookView xWindow="4044" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{AE2EE935-E2E8-4CB4-A33F-AA5BDDD6AC28}"/>
   </bookViews>
   <sheets>
-    <sheet name="QC Report (2)" sheetId="1" r:id="rId1"/>
+    <sheet name="جامع" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'QC Report (2)'!$B$1:$BE$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">جامع!$B$1:$BE$1</definedName>
     <definedName name="A6948.">#REF!</definedName>
     <definedName name="B" comment="YRYEE">#REF!</definedName>
     <definedName name="FDFS">#REF!</definedName>
@@ -49,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="77">
   <si>
     <t>تاریخ</t>
   </si>
@@ -222,9 +219,6 @@
     <t>هدف عظام</t>
   </si>
   <si>
-    <t>اطلاعات جامع کیفیت حین تولید</t>
-  </si>
-  <si>
     <t>تاریخ سفارش</t>
   </si>
   <si>
@@ -277,6 +271,16 @@
   </si>
   <si>
     <t>بازرس مسبب ایراد</t>
+  </si>
+  <si>
+    <t>اطلاعات جامع کیفیت حین تولید
+و عیب های سند بازرسی</t>
+  </si>
+  <si>
+    <t>تعداد تولید به تفکیک سند عملکرد</t>
+  </si>
+  <si>
+    <t>مقدار سالم</t>
   </si>
 </sst>
 </file>
@@ -497,7 +501,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -518,40 +522,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="QC Report اسفند"/>
-      <sheetName val="QC Report (4)"/>
-      <sheetName val="QC Report (3)"/>
-      <sheetName val="Sheet2"/>
-      <sheetName val="QC Report (2)"/>
-      <sheetName val="Sheet1 (2)"/>
-      <sheetName val="Sheet4"/>
-      <sheetName val="Sheet3"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="QC Report"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -820,7 +790,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:BE2"/>
+  <dimension ref="A1:BE3"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
@@ -1050,14 +1020,14 @@
       </c>
     </row>
     <row r="2" spans="1:57" s="19" customFormat="1" ht="66" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>57</v>
-      </c>
       <c r="C2" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>3</v>
@@ -1066,40 +1036,40 @@
         <v>4</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I2" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J2" s="16" t="s">
         <v>8</v>
       </c>
       <c r="K2" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="M2" s="16" t="s">
         <v>61</v>
-      </c>
-      <c r="M2" s="16" t="s">
-        <v>62</v>
       </c>
       <c r="N2" s="19">
         <v>0</v>
       </c>
       <c r="O2" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P2" s="16" t="s">
         <v>14</v>
       </c>
       <c r="Q2" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="R2" s="16" t="s">
         <v>16</v>
@@ -1108,37 +1078,37 @@
         <v>17</v>
       </c>
       <c r="T2" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="V2" s="18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="W2" s="18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="X2" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y2" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="Y2" s="16" t="s">
+      <c r="Z2" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="Z2" s="16" t="s">
+      <c r="AA2" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="AA2" s="16" t="s">
+      <c r="AB2" s="16" t="s">
         <v>68</v>
-      </c>
-      <c r="AB2" s="16" t="s">
-        <v>69</v>
       </c>
       <c r="AC2" s="16" t="s">
         <v>27</v>
       </c>
       <c r="AD2" s="18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AE2" s="16" t="s">
         <v>29</v>
@@ -1150,58 +1120,249 @@
         <v>31</v>
       </c>
       <c r="AH2" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI2" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="AI2" s="16" t="s">
+      <c r="AJ2" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="AJ2" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK2" s="18" t="s">
-        <v>58</v>
+      <c r="AK2" s="18">
+        <v>44000</v>
       </c>
       <c r="AL2" s="16" t="s">
         <v>36</v>
       </c>
       <c r="AM2" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN2" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="AO2" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="AP2" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="AQ2" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="AR2" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS2" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="AT2" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="AU2" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="AV2" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="AW2" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX2" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="AY2" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="AZ2" s="19">
+        <v>14000</v>
+      </c>
+      <c r="BA2" s="19">
+        <v>12000</v>
+      </c>
+      <c r="BB2" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="BC2" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="BD2" s="19">
+        <v>14000</v>
+      </c>
+      <c r="BE2" s="19">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
         <v>58</v>
       </c>
-      <c r="AN2" s="18" t="s">
+      <c r="G3" t="s">
         <v>58</v>
       </c>
-      <c r="AO2" s="18" t="s">
+      <c r="H3" t="s">
         <v>58</v>
       </c>
-      <c r="AP2" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ2" s="18" t="s">
+      <c r="I3" t="s">
         <v>58</v>
       </c>
-      <c r="AR2" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS2" s="18" t="s">
+      <c r="J3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>76</v>
+      </c>
+      <c r="O3" t="s">
         <v>58</v>
       </c>
-      <c r="AT2" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="AU2" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="AV2" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="AW2" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="AX2" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="AY2" s="18" t="s">
-        <v>58</v>
+      <c r="P3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>57</v>
+      </c>
+      <c r="R3" t="s">
+        <v>57</v>
+      </c>
+      <c r="S3" t="s">
+        <v>57</v>
+      </c>
+      <c r="T3" t="s">
+        <v>57</v>
+      </c>
+      <c r="U3" t="s">
+        <v>57</v>
+      </c>
+      <c r="V3" t="s">
+        <v>57</v>
+      </c>
+      <c r="W3" t="s">
+        <v>57</v>
+      </c>
+      <c r="X3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>44000</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AZ3">
+        <v>14000</v>
+      </c>
+      <c r="BA3">
+        <v>12000</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>57</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>57</v>
+      </c>
+      <c r="BD3">
+        <v>14000</v>
+      </c>
+      <c r="BE3">
+        <v>12000</v>
       </c>
     </row>
   </sheetData>
